--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Picture</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Affiliate Link</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1240,6 +1228,546 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pigeon Mio Nonstick Aluminum Cookware Gift Set, Includes Flat Tawa, Fry Pan, Kadai with Glass Lid, Kitchen Tool Set, Black, 8 Pieces</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61w2eRTCulL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C24BK3Z2?th=1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Material: Aluminium Blend | Color: Black | Style: Modern | Included Components: Cookware Set | Special Features: High Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pigeon Favourite 7 Piece Gift Set Non-Stick Coated Comes with Fry Pan, Kadhai, Lid, Sauce Pan, Spatula, Tadka Pan and a Tawa - Gas Stove Compatible (Red)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61aZ1CUskVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B073316W2J?th=1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Heat Resistant Bakelite Handles For Easy Grip | 7 Piece Forged Gift Set | Pure Coat Technology | 5 Layer Teflon Coating from Dupont USA | Chemical Pfoa Free And Scratch Resistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Kitchen Pride Non-Stick Cookware Set of 5 | Includes Nonstick Tawa, Frying Pan, Kadhai with Lid, Nylon Laddle &amp; Spatula | Non-Induction Base | Peach Color</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71rCioa7fGL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CSYYQ82J?th=1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | HEAT-RESISTANT HANDLE: Our cooking utensils comes with bakelite handle offers a secure, comfortable grip and stays cool for safe, easy cooking. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC : Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET: Color: Peach; Material: Aluminium; Package Content: 5 - Pieces Kitchen Pride Plus Non Induction Set . 1 Piece Non Stick Tawa 25cm, 1 Piece Fry Pan 24cm/1.6 litres, 1 Piece Kadhai with Glass Lid 24cm/2.5 litres, Nylon Laddle &amp; Spatula</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Induction Cookware &amp; Gas Stove Friendly Kitchen Jewel Set | 5 Pc Non-Stick Cookware Set | Kadhai with Lid, Fry Pan, Tawa, Laddle &amp; Spatula | Durable 5-Layer Non Stick Coating | Peach</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/711stZJUuFL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B5XRDRFH?th=1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | INDUCTION COOKWARE &amp; GAS STOVE FRIENDLY: Features a versatile base cooking utensils that ensures efficient, hassle-free cooking on both induction and gas cooktops. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC: Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET : Peach Colour ; Material: Aluminium; Package Content: 3 - Pieces Kitchen Jewel Set (1 - Piece Fry Pan, 24 cm; 1 - Piece Kadhai with Glass Lid, 24 cm; 1 - Piece Tawa, 25 cm 1 - Piece Nylon Laddle; 1 - Piece Nylon Spatula</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Fry Pan,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/719hJsjR3ZL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYBQB8T</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Fry Pan, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pigeon Aluminium Nonstick Duo Pack Flat Tawa 250 and Fry Pan 200 Gift Set (Red)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/510yXR4GoNL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>5 Layer Durable Nonstick Coating. Broiler :Safe | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Prestige Non-Stick 3 Pc Cookware Set with Stainless Steel Lid | Omega Select Plus | Omni Tawa 25cm | Fry Pan 25cm | Kadai 25cm | PFOA Free | Metal Spoon Friendly | Sturdy Handles | 1Y Warranty | ISI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51sTQ6mcf9L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00EICKVUA?th=1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗦𝗘𝗧: Includes Omni Tawa (25 cm), Fry Pan (25 cm), and Kadai (25 cm) with 1 Stainless Steel Lid (25 cm) — a complete everyday set for making dosas, stir-fries, curries, and sautéing. | 𝗦𝗨𝗣𝗘𝗥𝗜𝗢𝗥 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: High-quality aluminium cookware set with a non-stick coating that ensures residue-free cooking with less oil and easy food release. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free coating ensures healthy, toxin-free cooking every day. | 𝗦𝗖𝗥𝗔𝗧𝗖𝗛 &amp; 𝗔𝗕𝗥𝗔𝗦𝗜𝗢𝗡 𝗥𝗘𝗦𝗜𝗦𝗧𝗔𝗡𝗧 𝗧𝗘𝗖𝗛𝗡𝗢𝗟𝗢𝗚𝗬: Advanced coating resists scratches and corrosion on the non-stick surface, ensuring long-lasting durability and smooth performance. | 𝗠𝗘𝗧𝗔𝗟 𝗦𝗣𝗢𝗢𝗡 𝗙𝗥𝗜𝗘𝗡𝗗𝗟𝗬: Tough 3-layer coating withstands regular metal spoon use, keeping the surface safe and functional for years. | 𝗦𝗧𝗔𝗜𝗡𝗟𝗘𝗦𝗦 𝗦𝗧𝗘𝗘𝗟 𝗟𝗜𝗗: Flat-base Kadai comes with a durable stainless steel lid for safe cooking and easy serving. | 𝗚𝗔𝗦 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Suitable for gas stoves only. Ergonomic, heat-resistant handles provide a secure and comfortable grip. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟭-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and performance, backed by a 1-year Prestige warranty covering manufacturing defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Non-Stick 3 Pc Cookware Set with Glass Lid | 5-Layer Coating | Gas &amp; Induction Compatible | Omni Tawa 25cm | Fry Pan 24cm | Kadai 24cm | Crimson Red |2Y Warranty |ISI Certified</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51OUmYcUalL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DXRFR6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗖𝗢𝗠𝗕𝗢 𝗦𝗘𝗧: Includes Omni Tawa 25 cm, Fry Pan 24 cm, Kadai 24 cm, and a 24 cm Glass Lid—a complete everyday kit for dosas, stir-fries, curries, and sautéing. | 𝗜𝗡𝗗𝗜𝗔’𝗦 𝗙𝗜𝗥𝗦𝗧 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗪𝗜𝗧𝗛 𝟱-𝗟𝗔𝗬𝗘𝗥 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Designed using advanced German technology, the 5-layer non-stick coating ensures superior durability, long life, and metal-spoon friendliness. | 𝗗𝗨𝗥𝗔𝗕𝗟𝗘 𝗚𝗥𝗔𝗡𝗜𝗧𝗘-𝗙𝗜𝗡𝗜𝗦𝗛 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Stylish granite finish offers a premium look while providing a tough, scratch- and abrasion-resistant surface for lasting performance. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free non-stick coating ensures healthy, toxin-free meals every time. | 𝗧𝗪𝗢-𝗟𝗔𝗬𝗘𝗥 𝗠𝗘𝗧𝗔𝗟𝗟𝗜𝗖 𝗙𝗜𝗡𝗜𝗦𝗛 𝗘𝗫𝗧𝗘𝗥𝗜𝗢𝗥: Dual-layer metallic coating on the exterior maintains its elegant look even after extended use and repeated washing. | 𝗗𝗜𝗦𝗛𝗪𝗔𝗦𝗛𝗘𝗥 𝗦𝗔𝗙𝗘: Easy to clean and maintain — compatible with dishwashers for convenient, everyday use. | 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 𝗪𝗜𝗧𝗛 𝗚𝗔𝗦 &amp; 𝗜𝗡𝗗𝗨𝗖𝗧𝗜𝗢𝗡 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Works efficiently on both gas and induction cooktops. Ergonomically designed stay-cool handles ensure safe and comfortable handling. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟮-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and quality, backed by a 2-year Prestige warranty for assured reliability and peace of mind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Kitchen Pride Plus Granito I Set of 7 Non Stick Cookware | Non Induction I Cooking Pan, Kadhai with Lid, Tawa, Nylon Laddle &amp; Spatula I Peach Metallic</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713YqQo-9zL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DXQ1V29L?th=1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | HEAT-RESISTANT HANDLE: Our cooking utensils comes with bakelite handle offers a secure, comfortable grip and stays cool for safe, easy cooking. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC : Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET: Color: Peach Metallic; Material: Aluminium; Non Induction 7pc Set (Fry pan 24cm/1.6 LTR; Kadhai 24cm/2.5 LTR with Glass Lid; Tawa 25cm; 2 Nylon Laddle &amp; Spatula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wonderchef Valencia Non-Stick 4 Pc Cookware Set for Kitchen, Fry Pan 24cm, Kadhai with Glass Lid 24cm, Dosa Tawa 28cm, Non-Toxic PFOA Free, Gas Stove &amp; Induction Friendly, 2-Yr Warranty, Purple</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Qm7r1QfPL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09QPS9BDV?th=1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VERSATILE 4-PIECE SET - Kadhai with Lid 24 cm, Fry Pan 24 cm, Dosa Tawa 28 cm let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 100% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktopS, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Non-Stick 3 Pc Cookware Set with Glass Lid | 5-Layer Coating | Gas &amp; Induction Compatible | Omni Tawa 25cm | Fry Pan 24cm | Kadai 24cm | Moss Green | 2Y Warranty |ISI Certified</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Z62Y9QubL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DY7TPK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗖𝗢𝗠𝗕𝗢 𝗦𝗘𝗧: Includes Omni Tawa 25 cm, Fry Pan 24 cm, Kadai 24 cm, and a 24 cm Glass Lid—a complete everyday kit for dosas, stir-fries, curries, and sautéing. | 𝗜𝗡𝗗𝗜𝗔’𝗦 𝗙𝗜𝗥𝗦𝗧 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗪𝗜𝗧𝗛 𝟱-𝗟𝗔𝗬𝗘𝗥 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Designed using advanced German technology, the 5-layer non-stick coating ensures superior durability, long life, and metal-spoon | 𝗗𝗨𝗥𝗔𝗕𝗟𝗘 𝗚𝗥𝗔𝗡𝗜𝗧𝗘-𝗙𝗜𝗡𝗜𝗦𝗛 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Stylish granite finish offers a premium look while providing a tough, scratch- and abrasion-resistant surface for lasting performance. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free non-stick coating ensures healthy, toxin-free meals every time. | 𝗧𝗪𝗢-𝗟𝗔𝗬𝗘𝗥 𝗠𝗘𝗧𝗔𝗟𝗟𝗜𝗖 𝗙𝗜𝗡𝗜𝗦𝗛 𝗘𝗫𝗧𝗘𝗥𝗜𝗢𝗥: Dual-layer metallic coating on the exterior maintains its elegant look even after extended use and repeated washing. | 𝗗𝗜𝗦𝗛𝗪𝗔𝗦𝗛𝗘𝗥 𝗦𝗔𝗙𝗘: Easy to clean and maintain — compatible with dishwashers for convenient, everyday use. | 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 𝗪𝗜𝗧𝗛 𝗚𝗔𝗦 &amp; 𝗜𝗡𝗗𝗨𝗖𝗧𝗜𝗢𝗡 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Works efficiently on both gas and induction cooktops. Ergonomically designed stay-cool handles ensure safe and comfortable handling. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟮-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and quality, backed by a 2-year Prestige warranty for assured reliability and peace of mind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo 6 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25cm Tawa, 22 cm Kadai, 22cm Fry Pan, 1 Glass Lid &amp; 2 Nylon Spatulas | Grey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61etK-QYt+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYCF584?th=1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Impex 6 Pcs Nonstick Granite Cookware Set | 3mm Thick Induction Base | Kadai with Glass Lid, Frypan, Tawa, Tadka Pan &amp; Milk Pan | Gas &amp; Induction Compatible Cookware Set | PFOA Free | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612471TQz1L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CX4KLN26</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟔-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Includes 240mm Kadai with Glass Lid, 240mm Frypan, 240mm Tawa, 160mm Milk Pan &amp; 90mm Tadka Pan – handles frying, sautéing, tempering, dosa-making, curries &amp; warming milk in one set. | 💎 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Advanced granite nonstick coating ensures superior heat retention, even cooking &amp; long-lasting nonstick performance – less oil needed for healthier, tastier everyday meals. | 🔥 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Induction bottom base works seamlessly across gas stoves, induction cooktops &amp; electric hobs, giving you complete flexibility to cook anywhere in a modern or traditional Indian kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄, 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂 &amp; 𝐅𝐎𝐎𝐃 𝐒𝐀𝐅𝐄: Premium nonstick granite coating is completely PFOA free, ensuring a safer cooking surface with no harmful chemical leaching into your family's food, meal after meal. | ✋ 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐂𝐇𝐑𝐎𝐌𝐄 𝐏𝐋𝐀𝐓𝐄𝐃 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy chrome-plated mounted handles with detachable knobs plus stainless steel wire handles give a secure, cool-touch grip, easy maneuverability &amp; compact space-saving storage. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖-𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Super granite nonstick surface with even heat distribution lets you cook flavourful, nutritious meals using minimal oil, cutting down fat while keeping every dish deliciously moist and evenly cooked. | 🧽 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓 𝐒𝐔𝐑𝐅𝐀𝐂𝐄: The tough nonstick granite coating resists scratching from daily use and wipes clean effortlessly, saving you time and effort on kitchen cleanup after every meal. | 🍽️ 𝐀𝐋𝐋-𝐈𝐍-𝐎𝐍𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 &amp; 𝐌𝐔𝐋𝐓𝐈-𝐂𝐔𝐈𝐒𝐈𝐍𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Kadai for curries &amp; deep frying, Tawa for dosa/roti, Tadka Pan for tempering spices, Frypan for sauteing &amp; Milk Pan for boiling – one set for your entire kitchen. | 🎁 𝐏𝐄𝐑𝐅𝐄𝐂𝐓 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍: An elegant, practical cookware gift set ideal for weddings, housewarmings, festivals &amp; new home kitchens – a thoughtful present that upgrades everyday cooking instantly. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐁𝐔𝐈𝐋𝐃: Backed by Impex's 1-year manufacturer warranty, this rust-resistant, long-lasting cookware set is engineered for reliable daily performance in Indian households for years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 6 Piece Non-Stick Cookware Set with Detachable Handle| Granite Finish | Induction Base | Pfoa Free | HTR Exterior Coating | Black</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61WoqAJEnIL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZW8NVFN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/812-MTsU4AL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41BFBBB?th=1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Elegant white marble finish enhances kitchen aesthetics | Induction base suitable for gas stove and induction cooktops | Superior nonstick coating prevents food sticking | Saves cooking oil for healthier meals | Strong and sturdy construction for regular use</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Prestige Omega Deluxe Granite Aluminium 3 Pcs Set- Tawa, Fry Pan &amp; Kadai with 1 Glass Lid|Non-Stick|Spatter-Coated Surface|Induction &amp; Gas Compatible|Black</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/617m8cRiYkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01H932RC4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Made using German technology and it lasts three times longer than ordinary non-stick cookware. | Special spatter-coated surface looks new for longer and is also metal-spoon friendly | Can be used on both gas and induction cook-tops. | Durable Granite-finish Coating Dishwasher Safe Superior Non-stick Surface Cook &amp; Serve | Warranty : 2 Years Manufacturer Warranty</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DOZY 5-Piece Non-Stick Cookware Combo Set with Kadhai, Tawa &amp; Tadka Pan Induction Bottom Non-Stick Coated Cookware Set (Iron-Rich Nonstick Cookware Combo)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61V9hrdORHL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1WBB126?th=1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>COMPLETE 5-PIECE SET: Includes a Kadhai, Tawa, Tadka Pan, and additional cookware pieces to cover all your everyday Indian cooking needs. | PREMIUM NON-STICK COATING: Superior non-stick surface ensures food slides off effortlessly, making cooking and cleaning quick and hassle-free. | INDUCTION COMPATIBLE: Specially designed with an induction-friendly bottom, making this cookware set compatible with all types of cooktops. | ERGONOMIC HANDLES: Fitted with sturdy, heat-resistant handles for a secure and comfortable grip while cooking, ensuring safe handling at all times. | DURABLE CONSTRUCTION: Handcrafted from high-quality materials with even heat distribution for consistent, perfectly cooked results every time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hawkins Futura 5 Pieces Cookware Set 4 - Non Stick Kadhai, Two Frying Pans, Saucepan, Saute Pan and Two Glass Lids, Black (NSET4)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61T0Fe6un2S._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00EVR0CRY?th=1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consists two Frying Pans, Deep-Fry Pan (Stir-Fry Pan), Saucepan with glass lid and Curry Pan (Sauté Pan) with glass lid to cater to most of your cooking needs | There is attractive saving on the purchase of the Set when compared with buying individual items separately | Each item included in the Set is accompanied by its own Instruction Manual / Cookbook and its own Guarantee Card | Suitable for use on domestic gas, electric, ceramic and halogen stoves</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Prestige Omega Deluxe Non-Stick Cookware 3 Pc Set |PFOA Free 5-Layer Coating | Omni Tawa 25 cm | Fry Pan 24 cm | Kadai with Glass Lid 24 cm | Brown | Dishwasher Safe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61eTcL4tdkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DY7TD6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>India's First Non-Stick Cookware with 5-Layers Coating | Durable Granite-finish Coating | Two-layer Metallic Finish Exterior | Superior Non-stick Surface | Dishwasher Safe | Stay-cool Bakelite Handles | Gas Stove and Induction Compatible | PFOA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 11 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 3 Containers | 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71VFfXMdmeL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41FL5NG?th=1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Complete cookware set for versatile cooking requirements | Induction and gas stove compatible base | Elegant white marble nonstick interior and exterior | Even heat distribution for faster cooking | Heat resistant handles for safe and easy use</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,546 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pigeon Mio Nonstick Aluminum Cookware Gift Set, Includes Flat Tawa, Fry Pan, Kadai with Glass Lid, Kitchen Tool Set, Black, 8 Pieces</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61w2eRTCulL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C24BK3Z2?th=1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Material: Aluminium Blend | Color: Black | Style: Modern | Included Components: Cookware Set | Special Features: High Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Induction Cookware &amp; Gas Stove Friendly Kitchen Jewel Set | 5 Pc Non-Stick Cookware Set | Kadhai with Lid, Fry Pan, Tawa, Laddle &amp; Spatula | Durable 5-Layer Non Stick Coating | Peach</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/711stZJUuFL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B5XRDRFH?th=1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | INDUCTION COOKWARE &amp; GAS STOVE FRIENDLY: Features a versatile base cooking utensils that ensures efficient, hassle-free cooking on both induction and gas cooktops. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC: Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET : Peach Colour ; Material: Aluminium; Package Content: 3 - Pieces Kitchen Jewel Set (1 - Piece Fry Pan, 24 cm; 1 - Piece Kadhai with Glass Lid, 24 cm; 1 - Piece Tawa, 25 cm 1 - Piece Nylon Laddle; 1 - Piece Nylon Spatula</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Kitchen Pride Non-Stick Cookware Set of 5 | Includes Nonstick Tawa, Frying Pan, Kadhai with Lid, Nylon Laddle &amp; Spatula | Non-Induction Base | Peach Color</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71rCioa7fGL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CSYYQ82J?th=1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | HEAT-RESISTANT HANDLE: Our cooking utensils comes with bakelite handle offers a secure, comfortable grip and stays cool for safe, easy cooking. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC : Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET: Color: Peach; Material: Aluminium; Package Content: 5 - Pieces Kitchen Pride Plus Non Induction Set . 1 Piece Non Stick Tawa 25cm, 1 Piece Fry Pan 24cm/1.6 litres, 1 Piece Kadhai with Glass Lid 24cm/2.5 litres, Nylon Laddle &amp; Spatula</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pigeon Favourite 7 Piece Gift Set Non-Stick Coated Comes with Fry Pan, Kadhai, Lid, Sauce Pan, Spatula, Tadka Pan and a Tawa - Gas Stove Compatible (Red)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61aZ1CUskVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B073316W2J?th=1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Heat Resistant Bakelite Handles For Easy Grip | 7 Piece Forged Gift Set | Pure Coat Technology | 5 Layer Teflon Coating from Dupont USA | Chemical Pfoa Free And Scratch Resistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Non-Stick 3 Pc Cookware Set with Glass Lid | 5-Layer Coating | Gas &amp; Induction Compatible | Omni Tawa 25cm | Fry Pan 24cm | Kadai 24cm | Crimson Red |2Y Warranty |ISI Certified</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51OUmYcUalL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DXRFR6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗖𝗢𝗠𝗕𝗢 𝗦𝗘𝗧: Includes Omni Tawa 25 cm, Fry Pan 24 cm, Kadai 24 cm, and a 24 cm Glass Lid—a complete everyday kit for dosas, stir-fries, curries, and sautéing. | 𝗜𝗡𝗗𝗜𝗔’𝗦 𝗙𝗜𝗥𝗦𝗧 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗪𝗜𝗧𝗛 𝟱-𝗟𝗔𝗬𝗘𝗥 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Designed using advanced German technology, the 5-layer non-stick coating ensures superior durability, long life, and metal-spoon friendliness. | 𝗗𝗨𝗥𝗔𝗕𝗟𝗘 𝗚𝗥𝗔𝗡𝗜𝗧𝗘-𝗙𝗜𝗡𝗜𝗦𝗛 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Stylish granite finish offers a premium look while providing a tough, scratch- and abrasion-resistant surface for lasting performance. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free non-stick coating ensures healthy, toxin-free meals every time. | 𝗧𝗪𝗢-𝗟𝗔𝗬𝗘𝗥 𝗠𝗘𝗧𝗔𝗟𝗟𝗜𝗖 𝗙𝗜𝗡𝗜𝗦𝗛 𝗘𝗫𝗧𝗘𝗥𝗜𝗢𝗥: Dual-layer metallic coating on the exterior maintains its elegant look even after extended use and repeated washing. | 𝗗𝗜𝗦𝗛𝗪𝗔𝗦𝗛𝗘𝗥 𝗦𝗔𝗙𝗘: Easy to clean and maintain — compatible with dishwashers for convenient, everyday use. | 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 𝗪𝗜𝗧𝗛 𝗚𝗔𝗦 &amp; 𝗜𝗡𝗗𝗨𝗖𝗧𝗜𝗢𝗡 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Works efficiently on both gas and induction cooktops. Ergonomically designed stay-cool handles ensure safe and comfortable handling. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟮-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and quality, backed by a 2-year Prestige warranty for assured reliability and peace of mind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Non-Stick 3 Pc Cookware Set with Glass Lid | 5-Layer Coating | Gas &amp; Induction Compatible | Omni Tawa 25cm | Fry Pan 24cm | Kadai 24cm | Moss Green | 2Y Warranty |ISI Certified</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Z62Y9QubL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DY7TPK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗖𝗢𝗠𝗕𝗢 𝗦𝗘𝗧: Includes Omni Tawa 25 cm, Fry Pan 24 cm, Kadai 24 cm, and a 24 cm Glass Lid—a complete everyday kit for dosas, stir-fries, curries, and sautéing. | 𝗜𝗡𝗗𝗜𝗔’𝗦 𝗙𝗜𝗥𝗦𝗧 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗪𝗜𝗧𝗛 𝟱-𝗟𝗔𝗬𝗘𝗥 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Designed using advanced German technology, the 5-layer non-stick coating ensures superior durability, long life, and metal-spoon | 𝗗𝗨𝗥𝗔𝗕𝗟𝗘 𝗚𝗥𝗔𝗡𝗜𝗧𝗘-𝗙𝗜𝗡𝗜𝗦𝗛 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Stylish granite finish offers a premium look while providing a tough, scratch- and abrasion-resistant surface for lasting performance. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free non-stick coating ensures healthy, toxin-free meals every time. | 𝗧𝗪𝗢-𝗟𝗔𝗬𝗘𝗥 𝗠𝗘𝗧𝗔𝗟𝗟𝗜𝗖 𝗙𝗜𝗡𝗜𝗦𝗛 𝗘𝗫𝗧𝗘𝗥𝗜𝗢𝗥: Dual-layer metallic coating on the exterior maintains its elegant look even after extended use and repeated washing. | 𝗗𝗜𝗦𝗛𝗪𝗔𝗦𝗛𝗘𝗥 𝗦𝗔𝗙𝗘: Easy to clean and maintain — compatible with dishwashers for convenient, everyday use. | 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 𝗪𝗜𝗧𝗛 𝗚𝗔𝗦 &amp; 𝗜𝗡𝗗𝗨𝗖𝗧𝗜𝗢𝗡 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Works efficiently on both gas and induction cooktops. Ergonomically designed stay-cool handles ensure safe and comfortable handling. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟮-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and quality, backed by a 2-year Prestige warranty for assured reliability and peace of mind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Prestige Non-Stick 3 Pc Cookware Set with Stainless Steel Lid | Omega Select Plus | Omni Tawa 25cm | Fry Pan 25cm | Kadai 25cm | PFOA Free | Metal Spoon Friendly | Sturdy Handles | 1Y Warranty | ISI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51sTQ6mcf9L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00EICKVUA?th=1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗦𝗘𝗧: Includes Omni Tawa (25 cm), Fry Pan (25 cm), and Kadai (25 cm) with 1 Stainless Steel Lid (25 cm) — a complete everyday set for making dosas, stir-fries, curries, and sautéing. | 𝗦𝗨𝗣𝗘𝗥𝗜𝗢𝗥 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: High-quality aluminium cookware set with a non-stick coating that ensures residue-free cooking with less oil and easy food release. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free coating ensures healthy, toxin-free cooking every day. | 𝗦𝗖𝗥𝗔𝗧𝗖𝗛 &amp; 𝗔𝗕𝗥𝗔𝗦𝗜𝗢𝗡 𝗥𝗘𝗦𝗜𝗦𝗧𝗔𝗡𝗧 𝗧𝗘𝗖𝗛𝗡𝗢𝗟𝗢𝗚𝗬: Advanced coating resists scratches and corrosion on the non-stick surface, ensuring long-lasting durability and smooth performance. | 𝗠𝗘𝗧𝗔𝗟 𝗦𝗣𝗢𝗢𝗡 𝗙𝗥𝗜𝗘𝗡𝗗𝗟𝗬: Tough 3-layer coating withstands regular metal spoon use, keeping the surface safe and functional for years. | 𝗦𝗧𝗔𝗜𝗡𝗟𝗘𝗦𝗦 𝗦𝗧𝗘𝗘𝗟 𝗟𝗜𝗗: Flat-base Kadai comes with a durable stainless steel lid for safe cooking and easy serving. | 𝗚𝗔𝗦 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Suitable for gas stoves only. Ergonomic, heat-resistant handles provide a secure and comfortable grip. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟭-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and performance, backed by a 1-year Prestige warranty covering manufacturing defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wonderchef Valencia Non-Stick 4 Pc Cookware Set for Kitchen, Fry Pan 24cm, Kadhai with Glass Lid 24cm, Dosa Tawa 28cm, Non-Toxic PFOA Free, Gas Stove &amp; Induction Friendly, 2-Yr Warranty, Purple</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Qm7r1QfPL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09QPS9BDV?th=1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VERSATILE 4-PIECE SET - Kadhai with Lid 24 cm, Fry Pan 24 cm, Dosa Tawa 28 cm let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 100% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktopS, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Prestige Omega Deluxe Non-Stick Cookware 3 Pc Set |PFOA Free 5-Layer Coating | Omni Tawa 25 cm | Fry Pan 24 cm | Kadai with Glass Lid 24 cm | Brown | Dishwasher Safe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61eTcL4tdkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DY7TD6</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>India's First Non-Stick Cookware with 5-Layers Coating | Durable Granite-finish Coating | Two-layer Metallic Finish Exterior | Superior Non-stick Surface | Dishwasher Safe | Stay-cool Bakelite Handles | Gas Stove and Induction Compatible | PFOA Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prestige Omega Deluxe Granite Aluminium 3 Pcs Set- Tawa, Fry Pan &amp; Kadai with 1 Glass Lid|Non-Stick|Spatter-Coated Surface|Induction &amp; Gas Compatible|Black</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/617m8cRiYkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01H932RC4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Made using German technology and it lasts three times longer than ordinary non-stick cookware. | Special spatter-coated surface looks new for longer and is also metal-spoon friendly | Can be used on both gas and induction cook-tops. | Durable Granite-finish Coating Dishwasher Safe Superior Non-stick Surface Cook &amp; Serve | Warranty : 2 Years Manufacturer Warranty</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Kitchen Pride Plus Granito I Set of 7 Non Stick Cookware | Non Induction I Cooking Pan, Kadhai with Lid, Tawa, Nylon Laddle &amp; Spatula I Peach Metallic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/713YqQo-9zL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DXQ1V29L?th=1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | HEAT-RESISTANT HANDLE: Our cooking utensils comes with bakelite handle offers a secure, comfortable grip and stays cool for safe, easy cooking. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC : Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET: Color: Peach Metallic; Material: Aluminium; Non Induction 7pc Set (Fry pan 24cm/1.6 LTR; Kadhai 24cm/2.5 LTR with Glass Lid; Tawa 25cm; 2 Nylon Laddle &amp; Spatula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/812-MTsU4AL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41BFBBB?th=1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Elegant white marble finish enhances kitchen aesthetics | Induction base suitable for gas stove and induction cooktops | Superior nonstick coating prevents food sticking | Saves cooking oil for healthier meals | Strong and sturdy construction for regular use</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo 6 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25cm Tawa, 22 cm Kadai, 22cm Fry Pan, 1 Glass Lid &amp; 2 Nylon Spatulas | Grey</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61etK-QYt+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYCF584?th=1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 6 Piece Non-Stick Cookware Set with Detachable Handle| Granite Finish | Induction Base | Pfoa Free | HTR Exterior Coating | Black</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61WoqAJEnIL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZW8NVFN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Impex Migo Nonstick Cookware Set 3 Pcs | Induction Bottom | 5 Layer Super Granite Coating | 3mm Thick Aluminium | PFOA Free | Gas &amp; Induction Compatible | Detachable Chrome Handle | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/713olRvDhHL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW3G6ZQC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>🍳 𝐀𝐃𝐕𝐀𝐍𝐂𝐄𝐃 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium non-stick surface is 10X tougher than ordinary coatings, delivering smooth food release, effortless everyday cooking and easy cleanup for busy Indian kitchens. | ⚡ 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄: Versatile induction bottom cookware works seamlessly across gas stoves, induction cooktops and other cooking surfaces, making it a flexible pick for modern and traditional kitchens alike. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖 𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free, non-toxic aluminium construction lets you cook nutritious, healthier meals with minimal oil, while keeping harmful chemicals away from your everyday family food and health. | 🔥 𝐎𝐏𝐓𝐈𝐌𝐀𝐋 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊𝐍𝐄𝐒𝐒: Sturdy 3mm thick aluminium body ensures even heat distribution, faster heating and consistent cooking results, preventing hot spots so every dish cooks evenly and thoroughly every time. | ✋ 𝐃𝐄𝐓𝐀𝐂𝐇𝐀𝐁𝐋𝐄 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄: Chrome-plated, sturdy detachable handle and knob provide a secure, comfortable grip while cooking, and allow for compact, space-saving storage in small, modern Indian kitchens. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓: Granite-finish non-stick surface is scratch resistant and simple to wipe clean, saving valuable time on daily kitchen chores while keeping the shine looking brand new. | 🍲 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑 𝐏𝐂𝐒 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Ideal for frying, sauteing, tadka, curries and everyday Indian cooking, this practical cookware set gives you the essential pans needed for a fully equipped modern kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄 &amp; 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂: Health-conscious, food-grade aluminium construction is completely free from PFOA and harmful chemicals, ensuring safe, worry-free cooking for you and your entire family, every day. | 💎 𝐌𝐈𝐑𝐑𝐎𝐑-𝐋𝐈𝐊𝐄 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐅𝐈𝐍𝐈𝐒𝐇: Elegant granite finish gives your cookware a premium, modern look that enhances your kitchen decor while offering long-lasting, durable non-stick performance you can trust daily. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Backed by a 1 year manufacturer warranty, this Impex nonstick cookware set is reliable, durable and a perfect gift choice for new homes, weddings and housewarmings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Impex 6 Pcs Nonstick Granite Cookware Set | 3mm Thick Induction Base | Kadai with Glass Lid, Frypan, Tawa, Tadka Pan &amp; Milk Pan | Gas &amp; Induction Compatible Cookware Set | PFOA Free | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/612471TQz1L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CX4KLN26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟔-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Includes 240mm Kadai with Glass Lid, 240mm Frypan, 240mm Tawa, 160mm Milk Pan &amp; 90mm Tadka Pan – handles frying, sautéing, tempering, dosa-making, curries &amp; warming milk in one set. | 💎 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Advanced granite nonstick coating ensures superior heat retention, even cooking &amp; long-lasting nonstick performance – less oil needed for healthier, tastier everyday meals. | 🔥 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Induction bottom base works seamlessly across gas stoves, induction cooktops &amp; electric hobs, giving you complete flexibility to cook anywhere in a modern or traditional Indian kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄, 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂 &amp; 𝐅𝐎𝐎𝐃 𝐒𝐀𝐅𝐄: Premium nonstick granite coating is completely PFOA free, ensuring a safer cooking surface with no harmful chemical leaching into your family's food, meal after meal. | ✋ 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐂𝐇𝐑𝐎𝐌𝐄 𝐏𝐋𝐀𝐓𝐄𝐃 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy chrome-plated mounted handles with detachable knobs plus stainless steel wire handles give a secure, cool-touch grip, easy maneuverability &amp; compact space-saving storage. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖-𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Super granite nonstick surface with even heat distribution lets you cook flavourful, nutritious meals using minimal oil, cutting down fat while keeping every dish deliciously moist and evenly cooked. | 🧽 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓 𝐒𝐔𝐑𝐅𝐀𝐂𝐄: The tough nonstick granite coating resists scratching from daily use and wipes clean effortlessly, saving you time and effort on kitchen cleanup after every meal. | 🍽️ 𝐀𝐋𝐋-𝐈𝐍-𝐎𝐍𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 &amp; 𝐌𝐔𝐋𝐓𝐈-𝐂𝐔𝐈𝐒𝐈𝐍𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Kadai for curries &amp; deep frying, Tawa for dosa/roti, Tadka Pan for tempering spices, Frypan for sauteing &amp; Milk Pan for boiling – one set for your entire kitchen. | 🎁 𝐏𝐄𝐑𝐅𝐄𝐂𝐓 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍: An elegant, practical cookware gift set ideal for weddings, housewarmings, festivals &amp; new home kitchens – a thoughtful present that upgrades everyday cooking instantly. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐁𝐔𝐈𝐋𝐃: Backed by Impex's 1-year manufacturer warranty, this rust-resistant, long-lasting cookware set is engineered for reliable daily performance in Indian households for years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cello Prima 3 pcs Non-Stick Aluminium Cookware Set, Cherry Red (28 cm Dosa Tawa, 22 cm Kadai with Glass Lid, 22 cm Fry Pan) | Induction Base, PFOA-Free, Sturdy Handles, Ideal for Gifting</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61YACQ7VkVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07H94YY16?th=1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Upgrade your everyday cooking with the Cello Prima Non-Stick Aluminium Cookware Set, featuring a stylish and modern finish that enhances the look of your kitchen while providing a practical and reliable solution for preparing a wide variety of meals for your family. | This versatile cookware set includes a 22 cm Kadhai with a durable glass lid, a 22 cm Fry Pan, and a spacious 28 cm Dosa Tawa, making it perfect for cooking curries, stir-fries, sautéed vegetables, dosas, pancakes, omelets, and many other delicious recipes with ease. | Crafted from high quality aluminium, each cookware piece delivers quick and even heat distribution to ensure consistent cooking results, reduce cooking time, and improve energy efficiency, allowing you to prepare meals more effectively every day. | The premium non-stick coating promotes healthier cooking by requiring less oil while preventing food from sticking to the surface, making cooking smoother and cleanup faster, while the dishwasher-safe construction adds extra convenience for busy households. | Designed with a sturdy induction-compatible base that works efficiently on both gas stoves and induction cooktops, this durable cookware set combines functionality, convenience, and long-lasting performance, making it an ideal choice for modern kitchens and everyday cooking needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|22 Cm Fry Pan,22 Cm Kadai,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71NSco75mOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYDWLMV</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 22 cm Fry Pan, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Judge by Prestige ACE Aluminium Non-Stick cookware BYK Set-Tawa 25cm-1U, Fry Pan 20cm-1U, Kadai 20cm-1U with Lid-1U + 3U Nylon Tools|Black</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71XddeECOFL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DG8N3MTV</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Durable Body | Low Oil Cooking | Elegant Design | Cool Touch Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Fry Pan,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/719hJsjR3ZL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYBQB8T</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Fry Pan, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,22 +829,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Impex Migo Nonstick Cookware Set 3 Pcs | Induction Bottom | 5 Layer Super Granite Coating | 3mm Thick Aluminium | PFOA Free | Gas &amp; Induction Compatible | Detachable Chrome Handle | 1 Yr Warranty</t>
+          <t>Impex 6 Pcs Nonstick Granite Cookware Set | 3mm Thick Induction Base | Kadai with Glass Lid, Frypan, Tawa, Tadka Pan &amp; Milk Pan | Gas &amp; Induction Compatible Cookware Set | PFOA Free | 1 Yr Warranty</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/713olRvDhHL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/612471TQz1L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CW3G6ZQC</t>
+          <t>https://www.amazon.in/dp/B0CX4KLN26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🍳 𝐀𝐃𝐕𝐀𝐍𝐂𝐄𝐃 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium non-stick surface is 10X tougher than ordinary coatings, delivering smooth food release, effortless everyday cooking and easy cleanup for busy Indian kitchens. | ⚡ 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄: Versatile induction bottom cookware works seamlessly across gas stoves, induction cooktops and other cooking surfaces, making it a flexible pick for modern and traditional kitchens alike. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖 𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free, non-toxic aluminium construction lets you cook nutritious, healthier meals with minimal oil, while keeping harmful chemicals away from your everyday family food and health. | 🔥 𝐎𝐏𝐓𝐈𝐌𝐀𝐋 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊𝐍𝐄𝐒𝐒: Sturdy 3mm thick aluminium body ensures even heat distribution, faster heating and consistent cooking results, preventing hot spots so every dish cooks evenly and thoroughly every time. | ✋ 𝐃𝐄𝐓𝐀𝐂𝐇𝐀𝐁𝐋𝐄 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄: Chrome-plated, sturdy detachable handle and knob provide a secure, comfortable grip while cooking, and allow for compact, space-saving storage in small, modern Indian kitchens. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓: Granite-finish non-stick surface is scratch resistant and simple to wipe clean, saving valuable time on daily kitchen chores while keeping the shine looking brand new. | 🍲 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑 𝐏𝐂𝐒 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Ideal for frying, sauteing, tadka, curries and everyday Indian cooking, this practical cookware set gives you the essential pans needed for a fully equipped modern kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄 &amp; 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂: Health-conscious, food-grade aluminium construction is completely free from PFOA and harmful chemicals, ensuring safe, worry-free cooking for you and your entire family, every day. | 💎 𝐌𝐈𝐑𝐑𝐎𝐑-𝐋𝐈𝐊𝐄 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐅𝐈𝐍𝐈𝐒𝐇: Elegant granite finish gives your cookware a premium, modern look that enhances your kitchen decor while offering long-lasting, durable non-stick performance you can trust daily. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Backed by a 1 year manufacturer warranty, this Impex nonstick cookware set is reliable, durable and a perfect gift choice for new homes, weddings and housewarmings.</t>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟔-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Includes 240mm Kadai with Glass Lid, 240mm Frypan, 240mm Tawa, 160mm Milk Pan &amp; 90mm Tadka Pan – handles frying, sautéing, tempering, dosa-making, curries &amp; warming milk in one set. | 💎 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Advanced granite nonstick coating ensures superior heat retention, even cooking &amp; long-lasting nonstick performance – less oil needed for healthier, tastier everyday meals. | 🔥 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Induction bottom base works seamlessly across gas stoves, induction cooktops &amp; electric hobs, giving you complete flexibility to cook anywhere in a modern or traditional Indian kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄, 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂 &amp; 𝐅𝐎𝐎𝐃 𝐒𝐀𝐅𝐄: Premium nonstick granite coating is completely PFOA free, ensuring a safer cooking surface with no harmful chemical leaching into your family's food, meal after meal. | ✋ 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐂𝐇𝐑𝐎𝐌𝐄 𝐏𝐋𝐀𝐓𝐄𝐃 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy chrome-plated mounted handles with detachable knobs plus stainless steel wire handles give a secure, cool-touch grip, easy maneuverability &amp; compact space-saving storage. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖-𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Super granite nonstick surface with even heat distribution lets you cook flavourful, nutritious meals using minimal oil, cutting down fat while keeping every dish deliciously moist and evenly cooked. | 🧽 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓 𝐒𝐔𝐑𝐅𝐀𝐂𝐄: The tough nonstick granite coating resists scratching from daily use and wipes clean effortlessly, saving you time and effort on kitchen cleanup after every meal. | 🍽️ 𝐀𝐋𝐋-𝐈𝐍-𝐎𝐍𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 &amp; 𝐌𝐔𝐋𝐓𝐈-𝐂𝐔𝐈𝐒𝐈𝐍𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Kadai for curries &amp; deep frying, Tawa for dosa/roti, Tadka Pan for tempering spices, Frypan for sauteing &amp; Milk Pan for boiling – one set for your entire kitchen. | 🎁 𝐏𝐄𝐑𝐅𝐄𝐂𝐓 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍: An elegant, practical cookware gift set ideal for weddings, housewarmings, festivals &amp; new home kitchens – a thoughtful present that upgrades everyday cooking instantly. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐁𝐔𝐈𝐋𝐃: Backed by Impex's 1-year manufacturer warranty, this rust-resistant, long-lasting cookware set is engineered for reliable daily performance in Indian households for years.</t>
         </is>
       </c>
     </row>
@@ -856,128 +856,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Impex 6 Pcs Nonstick Granite Cookware Set | 3mm Thick Induction Base | Kadai with Glass Lid, Frypan, Tawa, Tadka Pan &amp; Milk Pan | Gas &amp; Induction Compatible Cookware Set | PFOA Free | 1 Yr Warranty</t>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Fry Pan,1 Glass Lid|Grey</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/612471TQz1L._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/719hJsjR3ZL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CX4KLN26</t>
+          <t>https://www.amazon.in/dp/B0BZYBQB8T</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟔-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Includes 240mm Kadai with Glass Lid, 240mm Frypan, 240mm Tawa, 160mm Milk Pan &amp; 90mm Tadka Pan – handles frying, sautéing, tempering, dosa-making, curries &amp; warming milk in one set. | 💎 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Advanced granite nonstick coating ensures superior heat retention, even cooking &amp; long-lasting nonstick performance – less oil needed for healthier, tastier everyday meals. | 🔥 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Induction bottom base works seamlessly across gas stoves, induction cooktops &amp; electric hobs, giving you complete flexibility to cook anywhere in a modern or traditional Indian kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄, 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂 &amp; 𝐅𝐎𝐎𝐃 𝐒𝐀𝐅𝐄: Premium nonstick granite coating is completely PFOA free, ensuring a safer cooking surface with no harmful chemical leaching into your family's food, meal after meal. | ✋ 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐂𝐇𝐑𝐎𝐌𝐄 𝐏𝐋𝐀𝐓𝐄𝐃 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy chrome-plated mounted handles with detachable knobs plus stainless steel wire handles give a secure, cool-touch grip, easy maneuverability &amp; compact space-saving storage. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖-𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Super granite nonstick surface with even heat distribution lets you cook flavourful, nutritious meals using minimal oil, cutting down fat while keeping every dish deliciously moist and evenly cooked. | 🧽 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓 𝐒𝐔𝐑𝐅𝐀𝐂𝐄: The tough nonstick granite coating resists scratching from daily use and wipes clean effortlessly, saving you time and effort on kitchen cleanup after every meal. | 🍽️ 𝐀𝐋𝐋-𝐈𝐍-𝐎𝐍𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 &amp; 𝐌𝐔𝐋𝐓𝐈-𝐂𝐔𝐈𝐒𝐈𝐍𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Kadai for curries &amp; deep frying, Tawa for dosa/roti, Tadka Pan for tempering spices, Frypan for sauteing &amp; Milk Pan for boiling – one set for your entire kitchen. | 🎁 𝐏𝐄𝐑𝐅𝐄𝐂𝐓 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍: An elegant, practical cookware gift set ideal for weddings, housewarmings, festivals &amp; new home kitchens – a thoughtful present that upgrades everyday cooking instantly. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐁𝐔𝐈𝐋𝐃: Backed by Impex's 1-year manufacturer warranty, this rust-resistant, long-lasting cookware set is engineered for reliable daily performance in Indian households for years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cello Prima 3 pcs Non-Stick Aluminium Cookware Set, Cherry Red (28 cm Dosa Tawa, 22 cm Kadai with Glass Lid, 22 cm Fry Pan) | Induction Base, PFOA-Free, Sturdy Handles, Ideal for Gifting</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61YACQ7VkVL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B07H94YY16?th=1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Upgrade your everyday cooking with the Cello Prima Non-Stick Aluminium Cookware Set, featuring a stylish and modern finish that enhances the look of your kitchen while providing a practical and reliable solution for preparing a wide variety of meals for your family. | This versatile cookware set includes a 22 cm Kadhai with a durable glass lid, a 22 cm Fry Pan, and a spacious 28 cm Dosa Tawa, making it perfect for cooking curries, stir-fries, sautéed vegetables, dosas, pancakes, omelets, and many other delicious recipes with ease. | Crafted from high quality aluminium, each cookware piece delivers quick and even heat distribution to ensure consistent cooking results, reduce cooking time, and improve energy efficiency, allowing you to prepare meals more effectively every day. | The premium non-stick coating promotes healthier cooking by requiring less oil while preventing food from sticking to the surface, making cooking smoother and cleanup faster, while the dishwasher-safe construction adds extra convenience for busy households. | Designed with a sturdy induction-compatible base that works efficiently on both gas stoves and induction cooktops, this durable cookware set combines functionality, convenience, and long-lasting performance, making it an ideal choice for modern kitchens and everyday cooking needs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|22 Cm Fry Pan,22 Cm Kadai,1 Glass Lid|Grey</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71NSco75mOL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BZYDWLMV</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 22 cm Fry Pan, 22 cm Kadai, 1 Glass Lid</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Judge by Prestige ACE Aluminium Non-Stick cookware BYK Set-Tawa 25cm-1U, Fry Pan 20cm-1U, Kadai 20cm-1U with Lid-1U + 3U Nylon Tools|Black</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71XddeECOFL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DG8N3MTV</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Durable Body | Low Oil Cooking | Elegant Design | Cool Touch Handle</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Fry Pan,1 Glass Lid|Grey</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/719hJsjR3ZL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BZYBQB8T</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Fry Pan, 1 Glass Lid</t>
         </is>
